--- a/tests/fixtures/dominios/pesquisa_ambigua.xlsx
+++ b/tests/fixtures/dominios/pesquisa_ambigua.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,24 +477,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OBSERVACAO GERAL DO TRIMESTRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>10</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Excelente</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>46029</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
